--- a/artfynd/A 13605-2022 artfynd.xlsx
+++ b/artfynd/A 13605-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13605-2022 artfynd.xlsx
+++ b/artfynd/A 13605-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100367731</v>
+        <v>100367742</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>703502.8747755645</v>
+        <v>703389</v>
       </c>
       <c r="R2" t="n">
-        <v>7093606.845413984</v>
+        <v>7093519</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -790,12 +785,7 @@
         <v>100367732</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>703295.2718223379</v>
+        <v>703295</v>
       </c>
       <c r="R3" t="n">
-        <v>7093435.307909651</v>
+        <v>7093435</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100367730</v>
+        <v>100367733</v>
       </c>
       <c r="B4" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>703481.2786922791</v>
+        <v>703339</v>
       </c>
       <c r="R4" t="n">
-        <v>7093585.576134932</v>
+        <v>7093463</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100367727</v>
+        <v>100367734</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>703345.5889430963</v>
+        <v>703501</v>
       </c>
       <c r="R5" t="n">
-        <v>7093490.668244006</v>
+        <v>7093606</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1123,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100367764</v>
+        <v>100367740</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>703334.4895772927</v>
+        <v>703292</v>
       </c>
       <c r="R6" t="n">
-        <v>7093484.648920777</v>
+        <v>7093401</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,59 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100367738</v>
+        <v>100367727</v>
       </c>
       <c r="B7" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Balfors, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>703539.6053368576</v>
+        <v>703346</v>
       </c>
       <c r="R7" t="n">
-        <v>7093626.452721391</v>
+        <v>7093491</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100367753</v>
+        <v>100367730</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>703402.4086509172</v>
+        <v>703481</v>
       </c>
       <c r="R8" t="n">
-        <v>7093432.57194504</v>
+        <v>7093585</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1468,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100367752</v>
+        <v>100367731</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>703361.3172758021</v>
+        <v>703503</v>
       </c>
       <c r="R9" t="n">
-        <v>7093439.165815688</v>
+        <v>7093607</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1580,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100367761</v>
+        <v>100367764</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>703488.3307222852</v>
+        <v>703335</v>
       </c>
       <c r="R10" t="n">
-        <v>7093592.656333939</v>
+        <v>7093485</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1692,59 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100367747</v>
+        <v>100367765</v>
       </c>
       <c r="B11" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Balfors, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>703548.9406166634</v>
+        <v>703356</v>
       </c>
       <c r="R11" t="n">
-        <v>7093537.459719194</v>
+        <v>7093500</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1813,19 +1745,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100367769</v>
+        <v>100367766</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1853,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>703501.1144205391</v>
+        <v>703337</v>
       </c>
       <c r="R12" t="n">
-        <v>7093606.73071602</v>
+        <v>7093463</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1925,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100367756</v>
+        <v>100367768</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1965,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>703435.474072895</v>
+        <v>703351</v>
       </c>
       <c r="R13" t="n">
-        <v>7093488.13481417</v>
+        <v>7093461</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2037,37 +1959,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100367742</v>
+        <v>100367769</v>
       </c>
       <c r="B14" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>388</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>703389.2310692234</v>
+        <v>703501</v>
       </c>
       <c r="R14" t="n">
-        <v>7093519.552000321</v>
+        <v>7093607</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2149,37 +2066,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100367740</v>
+        <v>100367770</v>
       </c>
       <c r="B15" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2189,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>703292.6333330933</v>
+        <v>703515</v>
       </c>
       <c r="R15" t="n">
-        <v>7093401.148092519</v>
+        <v>7093579</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2261,15 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>100367757</v>
+        <v>100367771</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2277,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2301,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>703495.3872455957</v>
+        <v>703536</v>
       </c>
       <c r="R16" t="n">
-        <v>7093565.750188048</v>
+        <v>7093598</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2373,37 +2280,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>100367758</v>
+        <v>100367744</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2413,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>703280.5961031239</v>
+        <v>703520</v>
       </c>
       <c r="R17" t="n">
-        <v>7093395.950623314</v>
+        <v>7093529</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2485,15 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100367768</v>
+        <v>100367747</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2501,34 +2398,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Balfors, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>703351.0556344885</v>
+        <v>703549</v>
       </c>
       <c r="R18" t="n">
-        <v>7093461.009158464</v>
+        <v>7093537</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2597,50 +2503,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>100367765</v>
+        <v>100367750</v>
       </c>
       <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Balfors, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>703356.4593369446</v>
+        <v>703489</v>
       </c>
       <c r="R19" t="n">
-        <v>7093500.203844433</v>
+        <v>7093556</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2709,15 +2619,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>100367760</v>
+        <v>100367738</v>
       </c>
       <c r="B20" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2725,34 +2630,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Balfors, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>703361.0419625565</v>
+        <v>703540</v>
       </c>
       <c r="R20" t="n">
-        <v>7093450.182927811</v>
+        <v>7093626</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2821,37 +2735,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>100367733</v>
+        <v>100367751</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2861,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>703339.0010076336</v>
+        <v>703304</v>
       </c>
       <c r="R21" t="n">
-        <v>7093462.872768286</v>
+        <v>7093373</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2933,37 +2842,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>100367744</v>
+        <v>100367752</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2973,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>703519.883593736</v>
+        <v>703361</v>
       </c>
       <c r="R22" t="n">
-        <v>7093528.945339102</v>
+        <v>7093439</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3045,37 +2949,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>100367771</v>
+        <v>100367753</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3085,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>703536.1287405598</v>
+        <v>703402</v>
       </c>
       <c r="R23" t="n">
-        <v>7093598.419112736</v>
+        <v>7093432</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3160,12 +3059,7 @@
         <v>100367754</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3197,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>703405.0816224806</v>
+        <v>703405</v>
       </c>
       <c r="R24" t="n">
-        <v>7093452.609129</v>
+        <v>7093452</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3272,12 +3166,7 @@
         <v>100367755</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3309,10 +3198,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>703390.7550400476</v>
+        <v>703391</v>
       </c>
       <c r="R25" t="n">
-        <v>7093482.574124843</v>
+        <v>7093482</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3381,37 +3270,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>100367766</v>
+        <v>100367756</v>
       </c>
       <c r="B26" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3421,10 +3305,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>703336.800464174</v>
+        <v>703435</v>
       </c>
       <c r="R26" t="n">
-        <v>7093462.729513058</v>
+        <v>7093488</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3493,15 +3377,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>100367751</v>
+        <v>100367757</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,10 +3412,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>703304.1754780769</v>
+        <v>703496</v>
       </c>
       <c r="R27" t="n">
-        <v>7093373.207783135</v>
+        <v>7093566</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3605,37 +3484,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>100367734</v>
+        <v>100367758</v>
       </c>
       <c r="B28" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3645,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>703501.1716946226</v>
+        <v>703281</v>
       </c>
       <c r="R28" t="n">
-        <v>7093605.851684171</v>
+        <v>7093396</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3714,118 +3588,6 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>100367770</v>
-      </c>
-      <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Balfors, Ång</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>703514.4182461053</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7093578.907614117</v>
-      </c>
-      <c r="S29" t="n">
-        <v>5</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2022-04-30</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13605-2022 artfynd.xlsx
+++ b/artfynd/A 13605-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367742</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367732</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367733</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367734</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367740</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367727</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367730</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367731</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367764</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367765</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367766</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367768</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367769</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367770</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367771</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367744</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2500,6 +2585,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367747</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2616,6 +2706,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367750</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2732,6 +2827,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367738</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2839,6 +2939,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367751</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2946,6 +3051,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367752</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3053,6 +3163,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367753</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3160,6 +3275,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367754</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3267,6 +3387,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367755</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3374,6 +3499,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367756</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3481,6 +3611,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367757</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3588,8 +3723,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100367758</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>